--- a/InputData/trans/BPP/Battery Pack Price.xlsx
+++ b/InputData/trans/BPP/Battery Pack Price.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MeganMahajan\Documents\eps-us\InputData\trans\BPP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98B72860-0494-4188-8985-8F96BBF57E48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5ECB2E4-46DF-4367-A783-5F31E1460F20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{DC12087C-9A27-4A43-B4A9-6B3F1E517F08}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="10">
   <si>
     <t>Sources:</t>
   </si>
@@ -58,16 +58,13 @@
     <t>The EPS applies endogenous learning for battery pack prices in years where the battery pack price is listed as 0.</t>
   </si>
   <si>
-    <t>2025 to 2012</t>
-  </si>
-  <si>
-    <t>https://www.usinflationcalculator.com/</t>
-  </si>
-  <si>
-    <t>https://about.bnef.com/insights/clean-transport/lithium-ion-battery-pack-prices-fall-to-108-per-kilowatt-hour-despite-rising-metal-prices-bloombergnef/</t>
-  </si>
-  <si>
-    <t>Lithium-Ion Battery Pack Prices Fall to $108 Per Kilowatt-Hour, Despite Rising Metal Prices</t>
+    <t>Lithium-ion Battery Pack Prices Hit Record Low of $139/kWh</t>
+  </si>
+  <si>
+    <t>https://about.bnef.com/blog/lithium-ion-battery-pack-prices-hit-record-low-of-139-kwh/#:~:text=Given%20this%2C%20BNEF%20expects%20average,and%20%2480%2FkWh%20in%202030.</t>
+  </si>
+  <si>
+    <t>2023 to 2012</t>
   </si>
 </sst>
 </file>
@@ -442,19 +439,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF982137-6F01-4109-8226-D4C6F3731BA9}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.453125" customWidth="1"/>
-    <col min="2" max="2" width="101.26953125" customWidth="1"/>
+    <col min="1" max="1" width="19.42578125" customWidth="1"/>
+    <col min="2" max="2" width="101.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -462,43 +459,43 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B5" s="2">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B6" s="3" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B11" s="2">
-        <v>0.71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>8</v>
+        <v>0.75350342301658668</v>
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B6" r:id="rId1" location=":~:text=Given%20this%2C%20BNEF%20expects%20average,and%20%2480%2FkWh%20in%202030." xr:uid="{96C10B99-B75C-4A91-A1D1-2211BAD3764D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -508,109 +505,119 @@
   <sheetPr>
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AE2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
       <c r="B1">
+        <v>2021</v>
+      </c>
+      <c r="C1">
+        <v>2022</v>
+      </c>
+      <c r="D1">
+        <v>2023</v>
+      </c>
+      <c r="E1">
         <v>2024</v>
       </c>
-      <c r="C1">
+      <c r="F1">
         <v>2025</v>
       </c>
-      <c r="D1">
+      <c r="G1">
         <v>2026</v>
       </c>
-      <c r="E1">
+      <c r="H1">
         <v>2027</v>
       </c>
-      <c r="F1">
+      <c r="I1">
         <v>2028</v>
       </c>
-      <c r="G1">
+      <c r="J1">
         <v>2029</v>
       </c>
-      <c r="H1">
+      <c r="K1">
         <v>2030</v>
       </c>
-      <c r="I1">
+      <c r="L1">
         <v>2031</v>
       </c>
-      <c r="J1">
+      <c r="M1">
         <v>2032</v>
       </c>
-      <c r="K1">
+      <c r="N1">
         <v>2033</v>
       </c>
-      <c r="L1">
+      <c r="O1">
         <v>2034</v>
       </c>
-      <c r="M1">
+      <c r="P1">
         <v>2035</v>
       </c>
-      <c r="N1">
+      <c r="Q1">
         <v>2036</v>
       </c>
-      <c r="O1">
+      <c r="R1">
         <v>2037</v>
       </c>
-      <c r="P1">
+      <c r="S1">
         <v>2038</v>
       </c>
-      <c r="Q1">
+      <c r="T1">
         <v>2039</v>
       </c>
-      <c r="R1">
+      <c r="U1">
         <v>2040</v>
       </c>
-      <c r="S1">
+      <c r="V1">
         <v>2041</v>
       </c>
-      <c r="T1">
+      <c r="W1">
         <v>2042</v>
       </c>
-      <c r="U1">
+      <c r="X1">
         <v>2043</v>
       </c>
-      <c r="V1">
+      <c r="Y1">
         <v>2044</v>
       </c>
-      <c r="W1">
+      <c r="Z1">
         <v>2045</v>
       </c>
-      <c r="X1">
+      <c r="AA1">
         <v>2046</v>
       </c>
-      <c r="Y1">
+      <c r="AB1">
         <v>2047</v>
       </c>
-      <c r="Z1">
+      <c r="AC1">
         <v>2048</v>
       </c>
-      <c r="AA1">
+      <c r="AD1">
         <v>2049</v>
       </c>
-      <c r="AB1">
+      <c r="AE1">
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <f>118*About!B11</f>
-        <v>83.78</v>
+        <f>150*About!$B$11</f>
+        <v>113.025513452488</v>
       </c>
       <c r="C2">
-        <f>108*About!B11</f>
-        <v>76.679999999999993</v>
+        <f>161*About!$B$11</f>
+        <v>121.31405110567046</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <f>139*About!$B$11</f>
+        <v>104.73697579930555</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -682,6 +689,15 @@
         <v>0</v>
       </c>
       <c r="AB2">
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <v>0</v>
+      </c>
+      <c r="AE2">
         <v>0</v>
       </c>
     </row>
@@ -696,23 +712,23 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
       <c r="B1">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>2020</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
       <c r="B2">
-        <f>148*About!B11</f>
-        <v>105.08</v>
+        <f>160*About!B11</f>
+        <v>120.56054768265386</v>
       </c>
     </row>
   </sheetData>
